--- a/Result/profitability/3122.xlsx
+++ b/Result/profitability/3122.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM63"/>
+  <dimension ref="A1:AM64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.62</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.265</v>
+        <v>-0.2725</v>
       </c>
       <c r="N2" t="n">
-        <v>33.36875</v>
+        <v>33.5025</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>0.63</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.13875</v>
+        <v>-0.155</v>
       </c>
       <c r="N3" t="n">
-        <v>33.35625</v>
+        <v>33.06875</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>0.38</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.05249999999999995</v>
+        <v>-0.04124999999999995</v>
       </c>
       <c r="N4" t="n">
-        <v>33.22125</v>
+        <v>33.40375</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>0.3</v>
       </c>
       <c r="M5" t="n">
-        <v>0.05125000000000005</v>
+        <v>0.06125000000000005</v>
       </c>
       <c r="N5" t="n">
-        <v>33.585</v>
+        <v>33.60875</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
@@ -1137,10 +1137,10 @@
         <v>0.23</v>
       </c>
       <c r="M6" t="n">
-        <v>0.145</v>
+        <v>0.13875</v>
       </c>
       <c r="N6" t="n">
-        <v>33.76875</v>
+        <v>33.82125</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="M7" t="n">
-        <v>0.26375</v>
+        <v>0.2487500000000001</v>
       </c>
       <c r="N7" t="n">
-        <v>33.8125</v>
+        <v>33.58625</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -8433,6 +8433,133 @@
       </c>
       <c r="AM63" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>3122</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>81</v>
+      </c>
+      <c r="D64" t="n">
+        <v>54</v>
+      </c>
+      <c r="E64" t="n">
+        <v>27</v>
+      </c>
+      <c r="F64" t="n">
+        <v>33.01</v>
+      </c>
+      <c r="G64" t="n">
+        <v>-18</v>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>-22.63%</t>
+        </is>
+      </c>
+      <c r="I64" t="n">
+        <v>0</v>
+      </c>
+      <c r="J64" t="n">
+        <v>-18</v>
+      </c>
+      <c r="K64" t="n">
+        <v>-18</v>
+      </c>
+      <c r="L64" t="n">
+        <v>-0.44</v>
+      </c>
+      <c r="M64" t="n">
+        <v>-0.3975</v>
+      </c>
+      <c r="N64" t="n">
+        <v>33.565</v>
+      </c>
+      <c r="O64" t="n">
+        <v>0</v>
+      </c>
+      <c r="P64" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q64" t="n">
+        <v>0</v>
+      </c>
+      <c r="R64" t="n">
+        <v>0</v>
+      </c>
+      <c r="S64" t="n">
+        <v>0</v>
+      </c>
+      <c r="T64" t="n">
+        <v>0</v>
+      </c>
+      <c r="U64" t="n">
+        <v>0</v>
+      </c>
+      <c r="V64" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W64" t="n">
+        <v>-0.15</v>
+      </c>
+      <c r="X64" t="n">
+        <v>0.517241379310345</v>
+      </c>
+      <c r="Y64" t="n">
+        <v>-3.469999999999999</v>
+      </c>
+      <c r="Z64" t="n">
+        <v>-0.09512061403508765</v>
+      </c>
+      <c r="AA64" t="n">
+        <v>0.08000000000000002</v>
+      </c>
+      <c r="AB64" t="n">
+        <v>-0.1538461538461539</v>
+      </c>
+      <c r="AC64" t="n">
+        <v>0.1899999999999977</v>
+      </c>
+      <c r="AD64" t="n">
+        <v>0.005789152955514965</v>
+      </c>
+      <c r="AE64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF64" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH64" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI64" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ64" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK64" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL64" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM64" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
